--- a/public/plantillas/Plantilla Cursos PreAntartico.xlsx
+++ b/public/plantillas/Plantilla Cursos PreAntartico.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://escuelanaval-my.sharepoint.com/personal/jestadisticaplen_enap_edu_co/Documents/Estadística/Plantillas Xertify/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://escuelanaval-my.sharepoint.com/personal/jestadisticaplen_enap_edu_co/Documents/Estadística/Plantillas Xertify/Plantillas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="430" documentId="8_{36C02CF1-CC93-4962-AF9A-AB4F931B7064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3475764F-719E-4282-B0FD-190948F8AD7A}"/>
+  <xr:revisionPtr revIDLastSave="436" documentId="8_{36C02CF1-CC93-4962-AF9A-AB4F931B7064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7CEEEEC-9F66-411B-870A-7401BF1EF2E7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1113,7 +1113,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1262,7 +1262,6 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3832,10 +3831,10 @@
   <dimension ref="A1:Z35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5" defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.296875" style="53" customWidth="1"/>
-    <col min="2" max="2" width="25.296875" style="54" customWidth="1"/>
-    <col min="3" max="3" width="24" style="54" customWidth="1"/>
-    <col min="4" max="4" width="33.69921875" style="54" customWidth="1"/>
+    <col min="1" max="1" width="25.296875" style="52" customWidth="1"/>
+    <col min="2" max="2" width="25.296875" style="53" customWidth="1"/>
+    <col min="3" max="3" width="24" style="53" customWidth="1"/>
+    <col min="4" max="4" width="33.69921875" style="53" customWidth="1"/>
     <col min="5" max="5" width="28.3984375" style="3" customWidth="1"/>
     <col min="6" max="6" width="21.8984375" style="13" customWidth="1"/>
     <col min="7" max="7" width="21.59765625" style="8" hidden="1" customWidth="1"/>
@@ -4021,7 +4020,6 @@
       <c r="A3" s="49"/>
       <c r="B3" s="50"/>
       <c r="C3" s="51"/>
-      <c r="D3" s="52"/>
       <c r="E3" s="27"/>
       <c r="F3" s="23"/>
       <c r="G3" s="21"/>
@@ -4046,103 +4044,103 @@
       <c r="Z3" s="26"/>
     </row>
     <row r="4" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="55"/>
+      <c r="C4" s="54"/>
     </row>
     <row r="5" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="55"/>
+      <c r="C5" s="54"/>
     </row>
     <row r="6" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="55"/>
+      <c r="C6" s="54"/>
     </row>
     <row r="7" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="55"/>
+      <c r="C7" s="54"/>
     </row>
     <row r="8" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="55"/>
+      <c r="C8" s="54"/>
     </row>
     <row r="9" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="55"/>
+      <c r="C9" s="54"/>
     </row>
     <row r="10" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="55"/>
+      <c r="C10" s="54"/>
     </row>
     <row r="11" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C11" s="55"/>
+      <c r="C11" s="54"/>
     </row>
     <row r="12" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C12" s="55"/>
+      <c r="C12" s="54"/>
     </row>
     <row r="13" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="55"/>
+      <c r="C13" s="54"/>
     </row>
     <row r="14" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="55"/>
+      <c r="C14" s="54"/>
     </row>
     <row r="15" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="55"/>
+      <c r="C15" s="54"/>
     </row>
     <row r="16" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="55"/>
+      <c r="C16" s="54"/>
     </row>
     <row r="17" spans="3:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="55"/>
+      <c r="C17" s="54"/>
     </row>
     <row r="18" spans="3:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="55"/>
+      <c r="C18" s="54"/>
     </row>
     <row r="19" spans="3:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C19" s="55"/>
+      <c r="C19" s="54"/>
     </row>
     <row r="20" spans="3:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C20" s="55"/>
+      <c r="C20" s="54"/>
     </row>
     <row r="21" spans="3:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C21" s="55"/>
+      <c r="C21" s="54"/>
     </row>
     <row r="22" spans="3:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C22" s="55"/>
+      <c r="C22" s="54"/>
     </row>
     <row r="23" spans="3:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C23" s="55"/>
+      <c r="C23" s="54"/>
     </row>
     <row r="24" spans="3:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C24" s="55"/>
+      <c r="C24" s="54"/>
     </row>
     <row r="25" spans="3:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C25" s="55"/>
+      <c r="C25" s="54"/>
     </row>
     <row r="26" spans="3:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C26" s="55"/>
+      <c r="C26" s="54"/>
     </row>
     <row r="27" spans="3:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C27" s="55"/>
+      <c r="C27" s="54"/>
     </row>
     <row r="28" spans="3:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C28" s="55"/>
+      <c r="C28" s="54"/>
     </row>
     <row r="29" spans="3:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C29" s="55"/>
+      <c r="C29" s="54"/>
     </row>
     <row r="30" spans="3:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C30" s="55"/>
+      <c r="C30" s="54"/>
     </row>
     <row r="31" spans="3:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C31" s="55"/>
+      <c r="C31" s="54"/>
     </row>
     <row r="32" spans="3:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C32" s="55"/>
+      <c r="C32" s="54"/>
     </row>
     <row r="33" spans="3:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C33" s="55"/>
+      <c r="C33" s="54"/>
     </row>
     <row r="34" spans="3:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C34" s="55"/>
+      <c r="C34" s="54"/>
     </row>
     <row r="35" spans="3:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C35" s="55"/>
+      <c r="C35" s="54"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="z1WA+yjou5AcIlZZoznlt6OVP6LWzG0HGXNa/h+qij5L/qNp92PE4bJUFv4e4W1595I8w0SEMFQh/li2sEdIMw==" saltValue="6VYsaUJjZCTcNwm89NvWnA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="zsD+o2BrJwUip7IUnNIaDtHKzAlgXGpDx73WM5z+XO+xoaKjLQLXKmp4nYf930FjWg5wEHGeyxyO2ctd04TMMw==" saltValue="eRpu3A6e9jY2IDc5zq1HXw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
     <protectedRange sqref="C3:Z409" name="Rango1"/>
     <protectedRange sqref="A3:B422" name="Rango1_1"/>
@@ -4210,8 +4208,8 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D3" s="1" t="s">
